--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0007.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0007.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Squeezy Jelly ban đầu được phát triển như một loại thực phẩm bổ sung tiện lợi. Nó được thiết kế để mang theo dễ dàng, thích ứng linh hoạt và cung cấp tối đa dinh dưỡng chỉ trong một gói.</t>
+          <t>Thạch Nén Nhũ ban đầu được phát triển như một loại thực phẩm bổ sung tiện lợi. Nó được thiết kế để mang theo dễ dàng, thích ứng linh hoạt và cung cấp tối đa dinh dưỡng chỉ trong một gói.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Thế nên, như cậu thấy đấy, cuối cùng chúng ta không đủ thời gian phát triển để thêm hương vị. Mục tiêu "tùy biến" và "tiện lợi" có vẻ mâu thuẫn với nhau.</t>
+          <t>Thế nên, như cậu thấy đấy, cuối cùng chúng tao không đủ thời gian phát triển để thêm hương vị. Mục tiêu "tùy biến" và "tiện lợi" có vẻ mâu thuẫn với nhau.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Kế hoạch ban đầu là phối hợp với Spacetrek Collective để giải quyết chúng. Nhưng cậu đến trước và hành động nhanh hơn dự tính, giúp đồng đội của ta tránh khỏi thương vong.</t>
+          <t>Kế hoạch ban đầu là phối hợp với Tập Đoàn Spacetrek để giải quyết chúng. Nhưng cậu đến trước và hành động nhanh hơn dự tính, giúp đồng đội của ta tránh khỏi thương vong.</t>
         </is>
       </c>
     </row>
@@ -2787,8 +2787,8 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>THÔNG BÁO TUYỂN THÀNH VIÊN: "Collection Kẻ Săn Light" đang nhận bài dự thi!
-Câu lạc bộ Nhiếp ảnh Startorch Academy – Lightborne Horizons – tìm kiếm các học viên có thể ghi lại những điều kỳ diệu nhỏ bé trong cuộc sống học đường.
+          <t>THÔNG BÁO TUYỂN THÀNH VIÊN: "Bộ sưu tập Kẻ Săn Ánh Sáng" đang nhận bài dự thi!
+Câu lạc bộ Nhiếp ảnh Học viện Startorch – Lightborne Horizons – tìm kiếm các học viên có thể ghi lại những điều kỳ diệu nhỏ bé trong cuộc sống học đường.
 Dù bạn là tân sinh viên hay học viên cũ muốn lưu giữ kỷ niệm, chúng tôi mời tất cả những ai yêu thích việc săn đuổi ánh sáng và bóng tối cùng góp sức ghi lại những khoảnh khắc rực rỡ nhất của tuổi trẻ.
 Địa điểm đăng ký: Kho Lưu trữ Spacetrek, hàng ngày từ 12:00–14:00.</t>
         </is>
@@ -2858,8 +2858,8 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>THÔNG BÁO TUYỂN THÀNH VIÊN: "Collection Kẻ Săn Light" đang nhận bài dự thi!
-Câu lạc bộ Nhiếp ảnh Startorch Academy – Lightborne Horizons – tìm kiếm các học viên có thể ghi lại những điều kỳ diệu nhỏ bé trong cuộc sống học đường.
+          <t>THÔNG BÁO TUYỂN THÀNH VIÊN: "Bộ sưu tập Kẻ Săn Ánh Sáng" đang nhận bài dự thi!
+Câu lạc bộ Nhiếp ảnh Học viện Startorch – Lightborne Horizons – tìm kiếm các học viên có thể ghi lại những điều kỳ diệu nhỏ bé trong cuộc sống học đường.
 Dù bạn là tân sinh viên hay học viên cũ muốn lưu giữ kỷ niệm, chúng tôi mời tất cả những ai yêu thích việc săn đuổi ánh sáng và bóng tối cùng góp sức ghi lại những khoảnh khắc rực rỡ nhất của tuổi trẻ.
 Địa điểm đăng ký: Kho Lưu trữ Spacetrek, hàng ngày từ 12:00–14:00.</t>
         </is>
@@ -2929,8 +2929,8 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>THÔNG BÁO TUYỂN THÀNH VIÊN: "Collection Kẻ Săn Light" đang nhận bài dự thi!
-Câu lạc bộ Nhiếp ảnh Startorch Academy – Lightborne Horizons – tìm kiếm các học viên có thể ghi lại những điều kỳ diệu nhỏ bé trong cuộc sống học đường.
+          <t>THÔNG BÁO TUYỂN THÀNH VIÊN: "Bộ sưu tập Kẻ Săn Ánh Sáng" đang nhận bài dự thi!
+Câu lạc bộ Nhiếp ảnh Học viện Startorch – Lightborne Horizons – tìm kiếm các học viên có thể ghi lại những điều kỳ diệu nhỏ bé trong cuộc sống học đường.
 Dù bạn là tân sinh viên hay học viên cũ muốn lưu giữ kỷ niệm, chúng tôi mời tất cả những ai yêu thích việc săn đuổi ánh sáng và bóng tối cùng góp sức ghi lại những khoảnh khắc rực rỡ nhất của tuổi trẻ.
 Địa điểm đăng ký: Kho Lưu trữ Spacetrek, hàng ngày từ 12:00–14:00.</t>
         </is>
@@ -3000,8 +3000,8 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>THÔNG BÁO TUYỂN THÀNH VIÊN: "Collection Kẻ Săn Light" đang nhận bài dự thi!
-Câu lạc bộ Nhiếp ảnh Startorch Academy – Lightborne Horizons – tìm kiếm các học viên có thể ghi lại những điều kỳ diệu nhỏ bé trong cuộc sống học đường.
+          <t>THÔNG BÁO TUYỂN THÀNH VIÊN: "Bộ sưu tập Kẻ Săn Ánh Sáng" đang nhận bài dự thi!
+Câu lạc bộ Nhiếp ảnh Học viện Startorch – Lightborne Horizons – tìm kiếm các học viên có thể ghi lại những điều kỳ diệu nhỏ bé trong cuộc sống học đường.
 Dù bạn là tân sinh viên hay học viên cũ muốn lưu giữ kỷ niệm, chúng tôi mời tất cả những ai yêu thích việc săn đuổi ánh sáng và bóng tối cùng góp sức ghi lại những khoảnh khắc rực rỡ nhất của tuổi trẻ.
 Địa điểm đăng ký: Kho Lưu trữ Spacetrek, hàng ngày từ 12:00–14:00.</t>
         </is>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Còn về những tài liệu nội bộ bị rò rỉ... Chúng tôi đã xác minh, chỉ là nghiên cứu sơ bộ về Void Storm của Viện. Nội dung đã lỗi thời từ lâu.</t>
+          <t>Còn về những tài liệu nội bộ bị rò rỉ... Chúng tôi đã xác minh, chỉ là nghiên cứu sơ bộ về Bão Hư Không của Viện. Nội dung đã lỗi thời từ lâu.</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>Evans
-Nghề nghiệp: Viện Nghiên Cứu Spacetrek Collective - Trợ lý Nghiên cứu
+Nghề nghiệp: Viện Nghiên cứu Spacetrek Collective - Trợ lý Nghiên cứu
 Bí danh: Bóng Xám
 Vai trò: Truyền tải thông tin lịch trình nội bộ và phân công nhân sự
 Giao dịch gần nhất: ██████. Số tiền không rõ.
@@ -6648,7 +6648,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Những chiếc áo blouse trắng gọi đó là "nhiễu Void Storm tần số thấp." Nhưng những kẻ tin thì biết đó là linh hồn báo thù của một tiền bối gục ngã dưới áp lực, giờ đây mãi mãi gào thét trong đau đớn...</t>
+          <t>Những chiếc áo blouse trắng gọi đó là "nhiễu Bão Hư Không tần số thấp." Nhưng những kẻ tin thì biết đó là linh hồn báo thù của một tiền bối gục ngã dưới áp lực, giờ đây mãi mãi gào thét trong đau đớn...</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Cái gì tự dựng nên từ hư không? Một bản phát thanh phát vào 3 giờ sáng khi chẳng có ai ở đó? Con búp bê cứ quay về dù bạn có Dodgem nó đi bao xa? Tất cả những điều này đều đã được chúng tôi, Câu lạc bộ Nghiên cứu Huyền bí, ghi chép, điều tra và xác minh.</t>
+          <t>Cái gì tự dựng nên từ hư không? Một bản phát thanh phát vào 3 giờ sáng khi chẳng có ai ở đó? Con búp bê cứ quay về dù bạn có ném nó đi bao xa? Tất cả những điều này đều đã được chúng tôi, Câu lạc bộ Nghiên cứu Huyền bí, ghi chép, điều tra và xác minh.</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Đừng có mà nghĩ chỉ có chúng ta đang quan sát đâu. Những thứ siêu nhiên... chúng cũng đang nhìn lại. Và ngươi sẽ chẳng biết được khi nào chúng quyết định chìa tay ra hù ngươi đâu!</t>
+          <t>Đừng có mà nghĩ chỉ có chúng ta đang quan sát đâu. Những thứ siêu nhiên... chúng cũng đang nhìn lại. Và mày sẽ chẳng biết được khi nào chúng quyết định chìa tay ra hù mày đâu!</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>That's impossible. Sau khi cô ấy mất tích, chúng tôi đã tìm kiếm tín hiệu của cô khắp nơi. Không có gì cả. Chẳng một dấu vết. Thậm chí có người còn cho rằng cô ấy đã gặp phải Void Storm… hay một trong những truyền thuyết đô thị mà cô ấy đang theo đuổi.</t>
+          <t>Không thể nào. Sau khi cô ấy mất tích, chúng tôi đã tìm kiếm tín hiệu của cô khắp nơi. Không có gì cả. Chẳng một dấu vết. Thậm chí có người còn cho rằng cô ấy đã gặp phải Bão Hư Không… hay một trong những truyền thuyết đô thị mà cô ấy đang theo đuổi.</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Không đâu! Ta đang ngập đầu trong đống bài tập. Suốt ngày dính chặt trong phòng luôn. Từ chiều đến giờ ta còn chưa bước chân ra khỏi ký túc xá! Thôi thì số phận hội fan của ta giờ giao phó vào tay cậu vậy!</t>
+          <t>Không đâu! Tao đang ngập đầu trong đống bài tập. Suốt ngày dính chặt trong phòng luôn. Từ chiều đến giờ tao còn chưa bước chân ra khỏi ký túc xá! Thôi thì số phận hội fan của tao giờ giao phó vào tay cậu vậy!</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>The call ends. Cậu quay người rời đi, không hề hay biết rằng sâu trong đường hầm phía sau, một ánh sáng le lói chợt nhấp nháy trong bóng tối dần buông xuống, khi sương mù lại bắt đầu tụ lại.</t>
+          <t>Cuộc gọi kết thúc. Cậu quay người rời đi, không hề hay biết rằng sâu trong đường hầm phía sau, một ánh sáng le lói chợt nhấp nháy trong bóng tối dần buông xuống, khi sương mù lại bắt đầu tụ lại.</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Ta đang điều tra một vụ khác thì tình cờ phát hiện ra nó... Sương mù dày đặc, nhưng xuyên qua đó, ta thấy ánh sáng xanh nhợt nhạt. Cảm giác như đoàn tàu calling ta vậy.</t>
+          <t>Ta đang điều tra một vụ khác thì tình cờ phát hiện ra nó... Sương mù dày đặc, nhưng xuyên qua đó, ta thấy ánh sáng xanh nhợt nhạt. Cảm giác như đoàn tàu đang gọi ta vậy.</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Có nhiều tàn tích tương tự nằm rải rác khắp vùng băng giá. Hãy chú ý quan sát nhé. Nếu tìm thấy, nhớ báo ngay cho Startorch Academy ngay lập tức.</t>
+          <t>Có nhiều tàn tích tương tự nằm rải rác khắp vùng băng giá. Hãy chú ý quan sát nhé. Nếu tìm thấy, nhớ báo ngay cho Học viện Startorch ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Đầu tiên, phải qua Ủy ban Kiểm toán của Department, rồi đến Department trưởng phê duyệt, cuối cùng là Ban Giám hiệu Học viện. Nếu liên quan đến Roya, chúng ta còn phải gửi công hàm ngoại giao riêng.</t>
+          <t>Đầu tiên, phải qua Ủy ban Kiểm toán của Cục, rồi đến Cục trưởng phê duyệt, cuối cùng là Ban Giám hiệu Học viện. Nếu liên quan đến Roya, chúng ta còn phải gửi công hàm ngoại giao riêng.</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Có nhiều tàn tích tương tự nằm rải rác khắp vùng băng giá. Hãy chú ý quan sát nhé. Nếu tìm thấy, nhớ báo ngay cho Startorch Academy ngay lập tức.</t>
+          <t>Có nhiều tàn tích tương tự nằm rải rác khắp vùng băng giá. Hãy chú ý quan sát nhé. Nếu tìm thấy, nhớ báo ngay cho Học viện Startorch ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Đầu tiên, phải qua Ủy ban Kiểm toán của Department, rồi đến Department trưởng phê duyệt, cuối cùng là Ban Giám hiệu Học viện. Nếu liên quan đến Roya, chúng ta còn phải gửi công hàm ngoại giao riêng.</t>
+          <t>Đầu tiên, phải qua Ủy ban Kiểm toán của Cục, rồi đến Cục trưởng phê duyệt, cuối cùng là Ban Giám hiệu Học viện. Nếu liên quan đến Roya, chúng ta còn phải gửi công hàm ngoại giao riêng.</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Có nhiều tàn tích tương tự nằm rải rác khắp vùng băng giá. Hãy chú ý quan sát nhé. Nếu tìm thấy, nhớ báo ngay cho Startorch Academy ngay lập tức.</t>
+          <t>Có nhiều tàn tích tương tự nằm rải rác khắp vùng băng giá. Hãy chú ý quan sát nhé. Nếu tìm thấy, nhớ báo ngay cho Học viện Startorch ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Hah! Được rồi! Ta muốn mời ngươi gia nhập Icebreakers. Nhưng đó mới chỉ là bước đầu. Ngươi còn được hưởng địa vị và quyền hạn nhất định trong bang hội.</t>
+          <t>Haha! Được rồi! Tao muốn mời mày gia nhập Icebreakers. Nhưng đó mới chỉ là bước đầu. Mày còn được hưởng địa vị và quyền hạn nhất định trong bang hội.</t>
         </is>
       </c>
     </row>
@@ -9254,13 +9254,13 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Tiến Độ Build
+          <t>Tiến Độ Xây Dựng
 42/100
-Tiến Độ Build
+Tiến Độ Xây Dựng
 43/100
 ...
-Hmph Lại mấy kẻ Vô Lại cứ rên rỉ rằng băng quá mỏng, rằng nó sẽ chẳng bao giờ chịu nổi ánh mặt trời. Đồ ngu! Các ngươi chỉ xứng làm việc với gỗ và da thú! Nhìn tảng băng tuyệt vời này đi! Trong tay ta, nó trở nên cứng cáp và trong veo, giam giữ từng tia sáng. Đây mới là uy quyền ta đòi hỏi: tinh khiết đến mức tàn nhẫn, băng trong đến nỗi mỗi kẻ quỳ dưới chân nó đều phải nhìn thấy bóng dáng nỗi kinh hoàng của chính mình!
-High hơn! Xây cao hơn nữa! High đến mức ta sẽ trị vì trong im lặng, khi ngay cả bóng tối cũng phải run rẩy dưới ánh mắt của ta!</t>
+Hừ! Lại mấy kẻ Vô Lại cứ rên rỉ rằng băng quá mỏng, rằng nó sẽ chẳng bao giờ chịu nổi ánh mặt trời. Đồ ngu! Các ngươi chỉ xứng làm việc với gỗ và da thú! Nhìn tảng băng tuyệt vời này đi! Trong tay ta, nó trở nên cứng cáp và trong veo, giam giữ từng tia sáng. Đây mới là uy quyền ta đòi hỏi: tinh khiết đến mức tàn nhẫn, băng trong đến nỗi mỗi kẻ quỳ dưới chân nó đều phải nhìn thấy bóng dáng nỗi kinh hoàng của chính mình!
+Cao hơn! Xây cao hơn nữa! Cao đến mức ta sẽ trị vì trong im lặng, khi ngay cả bóng tối cũng phải run rẩy dưới ánh mắt của ta!</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Chỉ vì họ cho vài miếng ăn mà bắt chúng ta đi săn Frostbiter, rồi cắt những mảnh băng trên đầu chúng để trả nợ và đổi lấy đồ tiếp tế.</t>
+          <t>Chỉ vì họ cho vài miếng ăn mà bắt chúng tao đi săn Frostbiter, rồi cắt những mảnh băng trên đầu chúng để trả nợ và đổi lấy đồ tiếp tế.</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Đôi khi chúng tôi khó ngủ, và Edelschnees giúp ích cho việc đó. Ngươi có ý kiến gì à? Nghe cho rõ đây: đây là lời cảnh cáo cuối cùng của ta. Biến khỏi đây ngay!</t>
+          <t>Đôi khi chúng tôi khó ngủ, và Edelschnees giúp ích cho việc đó. Mày có ý kiến gì à? Nghe cho rõ đây: đây là lời cảnh cáo cuối cùng của tao. Biến khỏi đây ngay!</t>
         </is>
       </c>
     </row>
@@ -18092,7 +18092,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Bạn mở Terminal và xem lại những bức ảnh chụp máy ghi âm lúc trước để so sánh.
+          <t>Bạn mở Thiết bị đầu cuối và xem lại những bức ảnh chụp máy ghi âm lúc trước để so sánh.
 Khi phóng to, có thể thấy hai vết rãnh song song mờ nhạt trên vỏ máy.</t>
         </is>
       </c>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Nghe này, từ giờ trở đi cậu phải dừng việc này lại, được không? Khi ta kéo cậu lên khỏi hố băng đó, chỉ là vì đó là việc nên làm thôi. Ta đâu có mong đợi gì đâu.</t>
+          <t>Nghe này, từ giờ trở đi cậu phải dừng việc này lại, được không? Khi tao kéo cậu lên khỏi hố băng đó, chỉ là vì đó là việc nên làm thôi. Tao đâu có mong đợi gì đâu.</t>
         </is>
       </c>
     </row>
@@ -18418,7 +18418,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Nghe này, từ giờ trở đi cậu phải dừng việc này lại, được không? Khi ta kéo cậu lên khỏi hố băng đó, chỉ là vì đó là việc nên làm thôi. Ta đâu có mong đợi gì đâu.</t>
+          <t>Nghe này, từ giờ trở đi cậu phải dừng việc này lại, được không? Khi tao kéo cậu lên khỏi hố băng đó, chỉ là vì đó là việc nên làm thôi. Tao đâu có mong đợi gì đâu.</t>
         </is>
       </c>
     </row>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Hồi chơi game xây dựng, ta luôn đặt nhà cửa ở những nơi thế này, như những ẩn sĩ trong truyền thuyết Huanglong, hay giống các chủng tộc bí ẩn trong tiểu thuyết New Federation.</t>
+          <t>Hồi chơi game xây dựng, ta luôn đặt nhà cửa ở những nơi thế này, như những ẩn sĩ trong truyền thuyết Huanglong, hay giống các chủng tộc bí ẩn trong tiểu thuyết Liên Bang Mới.</t>
         </is>
       </c>
     </row>
@@ -21702,7 +21702,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Hệ thống báo đơn của cậu đã xong. Ta không muốn biết tại sao khẩu vị của cậu lại kỳ quặc thế, nhưng làm ơn đừng gọi mấy món lạ hoắc rồi không lấy nữa được không?!</t>
+          <t>Hệ thống báo đơn của cậu đã xong. Tao không muốn biết tại sao khẩu vị của cậu lại kỳ quặc thế, nhưng làm ơn đừng gọi mấy món lạ hoắc rồi không lấy nữa được không?!</t>
         </is>
       </c>
     </row>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Để ta kiểm tra tình trạng đã. Hmm... nguồn điện ổn định, nhưng nó vẫn liên tục ghi và xuất dữ liệu. Không biết đang gửi đi đâu nữa. Giống như cứ lặp đi lặp lại một yêu cầu y chang vậy.</t>
+          <t>Để ta kiểm tra tình trạng đã. Hừm... nguồn điện ổn định, nhưng nó vẫn liên tục ghi và xuất dữ liệu. Không biết đang gửi đi đâu nữa. Giống như cứ lặp đi lặp lại một yêu cầu y chang vậy.</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Bạn're {PlayerName}, right? Mình thuộc Câu lạc bộ Siêu nhiên. Chúng ta đã gặp nhau rồi, hồi còn cãi nhau xem có nên giải tán câu lạc bộ không... Ôi, may quá là cậu!</t>
+          <t>Cậu là {PlayerName}, phải không? Mình thuộc Câu lạc bộ Siêu nhiên. Chúng ta đã gặp nhau rồi, hồi còn cãi nhau xem có nên giải tán câu lạc bộ không... Ôi, may quá là cậu!</t>
         </is>
       </c>
     </row>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Nghe có vẻ căng thẳng lắm. Nhưng vấn đề là, việc điều quân tiếp viện cần thời gian. Sớm nhất cũng phải đợi đến lượt luân chuyển Echo tiếp theo.</t>
+          <t>Nghe có vẻ căng thẳng lắm. Nhưng vấn đề là, việc điều quân tiếp viện cần thời gian. Sớm nhất cũng phải đợi đến lượt luân chuyển Tổ Tacet tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -23132,7 +23132,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Theo tín hiệu tần số từ Starstack của cô ấy, dấu hiệu sinh tồn vẫn ổn định. Nhưng nơi này đầy rẫy Exoswarm đang hoành hành, mà cô ấy lại không phải chuyên gia chiến đấu. Ta lo là có chuyện gì đó đã xảy ra.</t>
+          <t>Theo tín hiệu tần số từ Starstack của cô ấy, dấu hiệu sinh tồn vẫn ổn định. Nhưng nơi này đầy rẫy Exoswarm đang hoành hành, mà cô ấy lại không phải chuyên gia chiến đấu. Tao lo là có chuyện gì đó đã xảy ra.</t>
         </is>
       </c>
     </row>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Ôi chết, cậu nói đúng. Chúng ta biến mất lâu quá rồi. Professor Maeve chắc đang phát điên lên mất. Và lũ Exoswarm đang hoành hành... Nếu chúng đột nhập vào trạm nghiên cứu, thì thảm họa thật rồi!</t>
+          <t>Ôi chết, cậu nói đúng. Chúng ta biến mất lâu quá rồi. Giáo sư Maeve chắc đang phát điên lên mất. Và lũ Exoswarm đang hoành hành... Nếu chúng đột nhập vào trạm nghiên cứu, thì thảm họa thật rồi!</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Suốt thời gian qua, lũ nhỏ đã kìm Dodgen nỗi buồn của riêng mình. Chúng biết ngày chia xa đang đến. Thế mà vẫn chuẩn bị quà cho tôi... Còn tôi... tôi cứ nghĩ chúng chỉ thích những thứ lấp lánh. Thật ngốc nghếch. Một Mục Đồng thật tệ hại.</t>
+          <t>Suốt thời gian qua, lũ nhỏ đã kìm nén nỗi buồn của riêng mình. Chúng biết ngày chia xa đang đến. Thế mà vẫn chuẩn bị quà cho tôi... Còn tôi... tôi cứ nghĩ chúng chỉ thích những thứ lấp lánh. Thật ngốc nghếch. Một Mục Đồng thật tệ hại.</t>
         </is>
       </c>
     </row>
@@ -30026,7 +30026,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Một danh hiệu đặc biệt... À, từ góc nhìn của Soliskin, mình muốn viết về Sáng Kiến Lumen. Họ... thực sự rất đặc biệt. Ồ! Mình sẽ đặt là: *"Beyond Bjartr Woods—Hành Trình Qua Mắt Soliskin."*</t>
+          <t>Một danh hiệu đặc biệt... À, từ góc nhìn của Soliskin, mình muốn viết về Sáng Kiến Lumen. Họ... thực sự rất đặc biệt. Ồ! Mình sẽ đặt là: *"Vượt Qua Bjartr Woods—Hành Trình Qua Mắt Soliskin."*</t>
         </is>
       </c>
     </row>
@@ -30221,7 +30221,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>&lt;ano=Hello&gt;Ni hao&lt;/ano&gt;, cô Linnea. Babu thường xuyên đến chơi với chúng tôi, nên chắc chắn rồi, tôi rất sẵn lòng giúp đỡ. Nhưng mà... tên tôi là Wenting, không phải Mao. Cô chắc chắn là tôi là học sinh cô đang tìm sao?</t>
+          <t>&lt;ano=Hello&gt;Ni hao&lt;/ano&gt;, cô Linnea. Babu thường xuyên đến chơi với tụi cháu, nên chắc chắn là vui lòng giúp đỡ ạ. Nhưng mà... cháu tên là Wenting, không phải Mao. Cô chắc cháu là học sinh cô đang tìm chứ ạ?</t>
         </is>
       </c>
     </row>
@@ -30351,7 +30351,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Con Gulpy này chắc đã đến Dimmr Plains từ lâu lắm rồi. Loài chúng bị ánh sáng từ Soliskin hấp dẫn tự nhiên. Và nơi nào có Soliskin tụ tập, thức ăn thường rất dồi dào...</t>
+          <t>Con Gulpy này chắc đã đến Đồng Bằng Dimmr từ lâu lắm rồi. Loài chúng bị ánh sáng từ Soliskin hấp dẫn tự nhiên. Và nơi nào có Soliskin tụ tập, thức ăn thường rất dồi dào...</t>
         </is>
       </c>
     </row>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Phỏng vấn tớ và Barton cho bài báo à? Ôi trời, dĩ nhiên rồi! Cậu muốn biết gì nào? Khoan—Khoan. Tớ không thể quyết định thay Barton được. Barton! Cậu có muốn tham gia phỏng vấn không?</t>
+          <t>Phỏng vấn tớ và Barton cho bài báo à? Ôi trời, dĩ nhiên rồi! Cậu muốn biết gì nào? Khoan—Đợi đã. Tớ không thể quyết định thay Barton được. Barton! Cậu có muốn tham gia phỏng vấn không?</t>
         </is>
       </c>
     </row>
@@ -30936,7 +30936,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Nghe có vẻ hơi viển vông, nhưng cậu lúc nào cũng khiến ta bất ngờ. Giống như lần không ai dám kích hoạt ma trận Lumescribe Component, nhưng cậu và {PlayerName} lại làm nó chạy ngon lành.</t>
+          <t>Nghe có vẻ hơi viển vông, nhưng cậu lúc nào cũng khiến tao bất ngờ. Giống như lần không ai dám kích hoạt ma trận Lumescribe Component, nhưng cậu và {PlayerName} lại làm nó chạy ngon lành.</t>
         </is>
       </c>
     </row>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Từ khi chuyển đến Startorch Academy để nghiên cứu, cuộc sống của tớ hoàn toàn bị chi phối bởi lịch trình mà mấy con TARD-E giao. Đến giờ tớ còn chẳng biết thời gian trôi qua thế nào nữa, haha.</t>
+          <t>Từ khi chuyển đến Học viện Startorch để nghiên cứu, cuộc sống của tớ hoàn toàn bị chi phối bởi lịch trình mà mấy con TARD-E giao. Đến giờ tớ còn chẳng biết thời gian trôi qua thế nào nữa, haha.</t>
         </is>
       </c>
     </row>
@@ -31131,7 +31131,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Nói đơn giản, tôi nghiên cứu về "siêu thực phẩm". Tôi đến Dimmr Plains để thu thập mẫu thực vật và động vật phục vụ phát triển thực phẩm. Và cả dữ liệu đột biến thức ăn trong môi trường khắc nghiệt.</t>
+          <t>Nói đơn giản, tôi nghiên cứu về "siêu thực phẩm". Tôi đến Đồng Bằng Dimmr để thu thập mẫu thực vật và động vật phục vụ phát triển thực phẩm. Và cả dữ liệu đột biến thức ăn trong môi trường khắc nghiệt.</t>
         </is>
       </c>
     </row>
@@ -31196,7 +31196,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Chuẩn luôn. Finella dúi vào tay ta một tờ giấy có tiêu đề *"Vai trò của Văn hóa Royan trong Kỹ thuật Chế biến Ẩm thực Phân tử New"* rồi chạy mất dép cùng Budee! Suýt chút nữa là ta đuổi cổ cô ta khỏi phòng thí nghiệm!</t>
+          <t>Chuẩn luôn. Finella dúi vào tay ta một tờ giấy có tiêu đề *"Vai trò của Văn hóa Royan trong Kỹ thuật Chế biến Ẩm thực Phân tử Mới"* rồi chạy mất dép cùng Budee! Suýt chút nữa là ta đuổi cổ cô ta khỏi phòng thí nghiệm!</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31586,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Professor Maeve từng nói rằng Soliskin sinh ra đã mang trong mình trí tuệ bẩm sinh mà ta không nên đánh giá thấp. Và tôi nghĩ, nếu họ đã đưa ra những lựa chọn xuất phát từ trái tim mình...</t>
+          <t>Giáo sư Maeve từng nói rằng Soliskin sinh ra đã mang trong mình trí tuệ bẩm sinh mà ta không nên đánh giá thấp. Và tôi nghĩ, nếu họ đã đưa ra những lựa chọn xuất phát từ trái tim mình...</t>
         </is>
       </c>
     </row>
@@ -31976,7 +31976,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Tọa độ đã gửi. Nhưng cẩn thận nhé, khu vực Solisia Landing có thể là cơn ác mộng để di chuyển. Hơn nữa, có báo cáo về bầy Exoswarm đang hoành hành ở đó. Những nạn nhân của những cơn Void Storm trước đây.</t>
+          <t>Tọa độ đã gửi. Nhưng cẩn thận nhé, khu vực Solisia Landing có thể là cơn ác mộng để di chuyển. Hơn nữa, có báo cáo về bầy Exoswarm đang hoành hành ở đó. Những nạn nhân của những cơn Bão Hư Không trước đây.</t>
         </is>
       </c>
     </row>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Học Viện đã hoàn thành khảo sát khu vực chính và mô hình hóa môi trường. Nhưng có bốn tàn tích thực vật cổ đại đang bất thường. Đó là ưu tiên hàng đầu. Tớ đã gửi tọa độ vào Terminal của cậu rồi.</t>
+          <t>Học Viện đã hoàn thành khảo sát khu vực chính và mô hình hóa môi trường. Nhưng có bốn tàn tích thực vật cổ đại đang bất thường. Đó là ưu tiên hàng đầu. Tớ đã gửi tọa độ vào Thiết bị đầu cuối của cậu rồi.</t>
         </is>
       </c>
     </row>
@@ -32496,7 +32496,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Nhưng khó khăn ở đây. Theo phân tích dữ liệu ngôn ngữ của ta, ngay cả những tương tác có thiện chí cũng có thể gây hại, nhất là khi cả hai bên đều không thực sự hiểu đối phương đang nói gì.</t>
+          <t>Nhưng khó khăn ở đây. Theo phân tích dữ liệu ngôn ngữ của tao, ngay cả những tương tác có thiện chí cũng có thể gây hại, nhất là khi cả hai bên đều không thực sự hiểu đối phương đang nói gì.</t>
         </is>
       </c>
     </row>
@@ -33081,7 +33081,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Một bài báo khoa học có tựa đề *"Mô hình Cấu trúc Địa chất Solaris Dựa trên Bề mặt Survey Dimmr Deep"*, với Zenus là tác giả chính và "{PlayerName}" là đồng tác giả thứ hai.</t>
+          <t>Một bài báo khoa học có tựa đề *"Mô hình Cấu trúc Địa chất Solaris Dựa trên Bề mặt Khảo sát Dimmr Deep"*, với Zenus là tác giả chính và "{PlayerName}" là đồng tác giả thứ hai.</t>
         </is>
       </c>
     </row>
@@ -33146,7 +33146,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Trước đây, ta chỉ có thể đứng nhìn từ xa khi các nhà nghiên cứu bước vào. Nhưng giờ, với tiến triển của Lumen Initiative, cuối cùng ta cũng có cơ hội đặt chân đến nơi này.</t>
+          <t>Trước đây, tao chỉ có thể đứng nhìn từ xa khi các nhà nghiên cứu bước vào. Nhưng giờ, với tiến triển của Lumen Initiative, cuối cùng tao cũng có cơ hội đặt chân đến nơi này.</t>
         </is>
       </c>
     </row>
